--- a/S15/T174/S15_T174_decision_7.xlsx
+++ b/S15/T174/S15_T174_decision_7.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="70">
   <si>
     <t xml:space="preserve">c1</t>
   </si>
@@ -133,70 +133,70 @@
     <t xml:space="preserve">Laying-off</t>
   </si>
   <si>
+    <t xml:space="preserve">Warsaw</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pack Purchasing</t>
   </si>
   <si>
     <t xml:space="preserve">x 1 batch</t>
   </si>
   <si>
+    <t xml:space="preserve">Budapest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puree Purchasing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x 1 bin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bucharest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrate Purchasing for Arnhem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cordial packaging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x 20 pallets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cordial production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bottle Purchasing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sugar Purchasing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x 1 tonne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrate Purchasing for Vesoul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCFFCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intercontinental transport</t>
+  </si>
+  <si>
     <t xml:space="preserve">Berlin</t>
   </si>
   <si>
-    <t xml:space="preserve">Puree Purchasing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x 1 bin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warsaw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrate Purchasing for Arnhem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bucharest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cordial packaging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x 20 pallets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cordial production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bottle Purchasing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sugar Purchasing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x 1 tonne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrate Purchasing for Vesoul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCFFCC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intercontinental transport</t>
-  </si>
-  <si>
     <t xml:space="preserve">Puree transport to Arnhem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Madrid</t>
   </si>
   <si>
     <t xml:space="preserve">Concentrate transport to Arnhem</t>
@@ -1571,7 +1571,9 @@
       <c r="C11" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="23"/>
+      <c r="D11" s="23" t="n">
+        <v>66</v>
+      </c>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
       <c r="G11" s="25"/>
@@ -1586,7 +1588,7 @@
         <v>26</v>
       </c>
       <c r="K11" s="28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L11" s="29" t="s">
         <v>27</v>
@@ -1603,7 +1605,9 @@
         <v>29</v>
       </c>
       <c r="D12" s="30"/>
-      <c r="E12" s="31"/>
+      <c r="E12" s="31" t="n">
+        <v>50</v>
+      </c>
       <c r="F12" s="31"/>
       <c r="G12" s="32"/>
       <c r="H12" s="26" t="str">
@@ -1617,7 +1621,7 @@
         <v>30</v>
       </c>
       <c r="K12" s="34" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L12" s="35" t="s">
         <v>31</v>
@@ -1647,9 +1651,7 @@
       <c r="J13" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="K13" s="34" t="n">
-        <v>0</v>
-      </c>
+      <c r="K13" s="34"/>
       <c r="L13" s="35" t="s">
         <v>35</v>
       </c>
@@ -1674,9 +1676,7 @@
       <c r="J14" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="34" t="n">
-        <v>0</v>
-      </c>
+      <c r="K14" s="34"/>
       <c r="L14" s="35" t="s">
         <v>35</v>
       </c>
@@ -1689,13 +1689,13 @@
         <v>25</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="31" t="n">
         <v>37</v>
       </c>
+      <c r="D15" s="31"/>
       <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
+      <c r="F15" s="31" t="n">
+        <v>10</v>
+      </c>
       <c r="G15" s="32"/>
       <c r="H15" s="26" t="str">
         <f aca="false">IF(AND(B15="",OR(C15&lt;&gt;"",D15&lt;&gt;"",E15&lt;&gt;"",F15&lt;&gt;"",G15&lt;&gt;"")),"A lorry must be selected",IF(AND(C15="",OR(D15&lt;&gt;"",E15&lt;&gt;"",F15&lt;&gt;"",G15&lt;&gt;"")),"A town must be selected",""))</f>
@@ -1705,13 +1705,13 @@
         <v>5</v>
       </c>
       <c r="J15" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K15" s="34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L15" s="35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1722,12 +1722,12 @@
         <v>25</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="31"/>
       <c r="E16" s="31"/>
       <c r="F16" s="31" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G16" s="32"/>
       <c r="H16" s="26" t="str">
@@ -1738,13 +1738,11 @@
         <v>6</v>
       </c>
       <c r="J16" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="K16" s="34" t="n">
-        <v>0</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="K16" s="34"/>
       <c r="L16" s="35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1755,12 +1753,12 @@
         <v>25</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" s="31"/>
       <c r="E17" s="31"/>
       <c r="F17" s="31" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G17" s="32"/>
       <c r="H17" s="26" t="str">
@@ -1771,13 +1769,11 @@
         <v>7</v>
       </c>
       <c r="J17" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="K17" s="43" t="n">
-        <v>0</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="K17" s="43"/>
       <c r="L17" s="44" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1788,12 +1784,12 @@
         <v>25</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="31" t="n">
-        <v>40</v>
-      </c>
-      <c r="E18" s="31"/>
+        <v>29</v>
+      </c>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31" t="n">
+        <v>50</v>
+      </c>
       <c r="F18" s="31"/>
       <c r="G18" s="32"/>
       <c r="H18" s="26" t="str">
@@ -1809,14 +1805,14 @@
         <v>25</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D19" s="31"/>
       <c r="E19" s="31"/>
-      <c r="F19" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="G19" s="32"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="32" t="n">
+        <v>10</v>
+      </c>
       <c r="H19" s="26" t="str">
         <f aca="false">IF(AND(B19="",OR(C19&lt;&gt;"",D19&lt;&gt;"",E19&lt;&gt;"",F19&lt;&gt;"",G19&lt;&gt;"")),"A lorry must be selected",IF(AND(C19="",OR(D19&lt;&gt;"",E19&lt;&gt;"",F19&lt;&gt;"",G19&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1833,14 +1829,14 @@
         <v>25</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D20" s="31"/>
       <c r="E20" s="31"/>
-      <c r="F20" s="31" t="n">
+      <c r="F20" s="31"/>
+      <c r="G20" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="G20" s="32"/>
       <c r="H20" s="26" t="str">
         <f aca="false">IF(AND(B20="",OR(C20&lt;&gt;"",D20&lt;&gt;"",E20&lt;&gt;"",F20&lt;&gt;"",G20&lt;&gt;"")),"A lorry must be selected",IF(AND(C20="",OR(D20&lt;&gt;"",E20&lt;&gt;"",F20&lt;&gt;"",G20&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1854,14 +1850,14 @@
         <v>25</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="31" t="n">
-        <v>42</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D21" s="31"/>
       <c r="E21" s="31"/>
       <c r="F21" s="31"/>
-      <c r="G21" s="32"/>
+      <c r="G21" s="32" t="n">
+        <v>20</v>
+      </c>
       <c r="H21" s="26" t="str">
         <f aca="false">IF(AND(B21="",OR(C21&lt;&gt;"",D21&lt;&gt;"",E21&lt;&gt;"",F21&lt;&gt;"",G21&lt;&gt;"")),"A lorry must be selected",IF(AND(C21="",OR(D21&lt;&gt;"",E21&lt;&gt;"",F21&lt;&gt;"",G21&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1870,30 +1866,22 @@
         <v>1</v>
       </c>
       <c r="J21" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="K21" s="28"/>
+      <c r="L21" s="45" t="s">
         <v>46</v>
-      </c>
-      <c r="K21" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="45" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B22" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="41" t="s">
-        <v>48</v>
-      </c>
+      <c r="B22" s="40"/>
+      <c r="C22" s="41"/>
       <c r="D22" s="31"/>
       <c r="E22" s="31"/>
-      <c r="F22" s="31" t="n">
-        <v>22</v>
-      </c>
+      <c r="F22" s="31"/>
       <c r="G22" s="32"/>
       <c r="H22" s="26" t="str">
         <f aca="false">IF(AND(B22="",OR(C22&lt;&gt;"",D22&lt;&gt;"",E22&lt;&gt;"",F22&lt;&gt;"",G22&lt;&gt;"")),"A lorry must be selected",IF(AND(C22="",OR(D22&lt;&gt;"",E22&lt;&gt;"",F22&lt;&gt;"",G22&lt;&gt;"")),"A town must be selected",""))</f>
@@ -1903,10 +1891,10 @@
         <v>2</v>
       </c>
       <c r="J22" s="46" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K22" s="34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L22" s="46" t="s">
         <v>31</v>
@@ -1917,16 +1905,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31" t="n">
-        <v>20</v>
-      </c>
+      <c r="E23" s="31" t="n">
+        <v>24</v>
+      </c>
+      <c r="F23" s="31"/>
       <c r="G23" s="32"/>
       <c r="H23" s="26" t="str">
         <f aca="false">IF(AND(B23="",OR(C23&lt;&gt;"",D23&lt;&gt;"",E23&lt;&gt;"",F23&lt;&gt;"",G23&lt;&gt;"")),"A lorry must be selected",IF(AND(C23="",OR(D23&lt;&gt;"",E23&lt;&gt;"",F23&lt;&gt;"",G23&lt;&gt;"")),"A town must be selected",""))</f>
@@ -1959,12 +1947,18 @@
       <c r="A24" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B24" s="40"/>
-      <c r="C24" s="41"/>
+      <c r="B24" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>33</v>
+      </c>
       <c r="D24" s="31"/>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
-      <c r="G24" s="32"/>
+      <c r="G24" s="32" t="n">
+        <v>24</v>
+      </c>
       <c r="H24" s="26" t="str">
         <f aca="false">IF(AND(B24="",OR(C24&lt;&gt;"",D24&lt;&gt;"",E24&lt;&gt;"",F24&lt;&gt;"",G24&lt;&gt;"")),"A lorry must be selected",IF(AND(C24="",OR(D24&lt;&gt;"",E24&lt;&gt;"",F24&lt;&gt;"",G24&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1984,10 +1978,16 @@
       <c r="A25" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B25" s="40"/>
-      <c r="C25" s="41"/>
+      <c r="B25" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="41" t="s">
+        <v>29</v>
+      </c>
       <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
+      <c r="E25" s="31" t="n">
+        <v>24</v>
+      </c>
       <c r="F25" s="31"/>
       <c r="G25" s="32"/>
       <c r="H25" s="26" t="str">
@@ -1998,13 +1998,11 @@
         <v>5</v>
       </c>
       <c r="J25" s="46" t="s">
-        <v>51</v>
-      </c>
-      <c r="K25" s="34" t="n">
-        <v>8</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="K25" s="34"/>
       <c r="L25" s="46" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2015,14 +2013,14 @@
         <v>32</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D26" s="31"/>
-      <c r="E26" s="31" t="n">
-        <v>18</v>
-      </c>
+      <c r="E26" s="31"/>
       <c r="F26" s="31"/>
-      <c r="G26" s="32"/>
+      <c r="G26" s="32" t="n">
+        <v>24</v>
+      </c>
       <c r="H26" s="26" t="str">
         <f aca="false">IF(AND(B26="",OR(C26&lt;&gt;"",D26&lt;&gt;"",E26&lt;&gt;"",F26&lt;&gt;"",G26&lt;&gt;"")),"A lorry must be selected",IF(AND(C26="",OR(D26&lt;&gt;"",E26&lt;&gt;"",F26&lt;&gt;"",G26&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2031,31 +2029,23 @@
         <v>6</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="K26" s="34" t="n">
-        <v>10</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="K26" s="34"/>
       <c r="L26" s="46" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B27" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="41" t="s">
-        <v>33</v>
-      </c>
+      <c r="B27" s="40"/>
+      <c r="C27" s="41"/>
       <c r="D27" s="31"/>
       <c r="E27" s="31"/>
       <c r="F27" s="31"/>
-      <c r="G27" s="32" t="n">
-        <v>18</v>
-      </c>
+      <c r="G27" s="32"/>
       <c r="H27" s="26" t="str">
         <f aca="false">IF(AND(B27="",OR(C27&lt;&gt;"",D27&lt;&gt;"",E27&lt;&gt;"",F27&lt;&gt;"",G27&lt;&gt;"")),"A lorry must be selected",IF(AND(C27="",OR(D27&lt;&gt;"",E27&lt;&gt;"",F27&lt;&gt;"",G27&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2064,13 +2054,11 @@
         <v>7</v>
       </c>
       <c r="J27" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="K27" s="43" t="n">
-        <v>0</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="K27" s="43"/>
       <c r="L27" s="47" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2078,23 +2066,23 @@
         <v>18</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C28" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="31" t="n">
-        <v>24</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="D28" s="31"/>
       <c r="E28" s="31"/>
       <c r="F28" s="31"/>
-      <c r="G28" s="32"/>
+      <c r="G28" s="32" t="n">
+        <v>25</v>
+      </c>
       <c r="H28" s="26" t="str">
         <f aca="false">IF(AND(B28="",OR(C28&lt;&gt;"",D28&lt;&gt;"",E28&lt;&gt;"",F28&lt;&gt;"",G28&lt;&gt;"")),"A lorry must be selected",IF(AND(C28="",OR(D28&lt;&gt;"",E28&lt;&gt;"",F28&lt;&gt;"",G28&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
       </c>
       <c r="J28" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2102,17 +2090,17 @@
         <v>19</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D29" s="31"/>
       <c r="E29" s="31"/>
-      <c r="F29" s="31" t="n">
-        <v>24</v>
-      </c>
-      <c r="G29" s="32"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="32" t="n">
+        <v>25</v>
+      </c>
       <c r="H29" s="26" t="str">
         <f aca="false">IF(AND(B29="",OR(C29&lt;&gt;"",D29&lt;&gt;"",E29&lt;&gt;"",F29&lt;&gt;"",G29&lt;&gt;"")),"A lorry must be selected",IF(AND(C29="",OR(D29&lt;&gt;"",E29&lt;&gt;"",F29&lt;&gt;"",G29&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2122,10 +2110,16 @@
       <c r="A30" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B30" s="40"/>
-      <c r="C30" s="41"/>
+      <c r="B30" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>29</v>
+      </c>
       <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
+      <c r="E30" s="31" t="n">
+        <v>20</v>
+      </c>
       <c r="F30" s="31"/>
       <c r="G30" s="32"/>
       <c r="H30" s="26" t="str">
@@ -2143,13 +2137,13 @@
         <v>21</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C31" s="41" t="s">
         <v>22</v>
       </c>
       <c r="D31" s="31" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E31" s="31"/>
       <c r="F31" s="31"/>
@@ -2164,17 +2158,19 @@
         <v>22</v>
       </c>
       <c r="B32" s="40" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C32" s="41" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D32" s="31"/>
-      <c r="E32" s="31" t="n">
-        <v>14</v>
-      </c>
-      <c r="F32" s="31"/>
-      <c r="G32" s="32"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31" t="n">
+        <v>42</v>
+      </c>
+      <c r="G32" s="32" t="n">
+        <v>20</v>
+      </c>
       <c r="H32" s="26" t="str">
         <f aca="false">IF(AND(B32="",OR(C32&lt;&gt;"",D32&lt;&gt;"",E32&lt;&gt;"",F32&lt;&gt;"",G32&lt;&gt;"")),"A lorry must be selected",IF(AND(C32="",OR(D32&lt;&gt;"",E32&lt;&gt;"",F32&lt;&gt;"",G32&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2183,33 +2179,25 @@
         <v>1</v>
       </c>
       <c r="J32" s="49" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L32" s="49" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B33" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>58</v>
-      </c>
+      <c r="B33" s="40"/>
+      <c r="C33" s="41"/>
       <c r="D33" s="31"/>
       <c r="E33" s="31"/>
-      <c r="F33" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="G33" s="32" t="n">
-        <v>14</v>
-      </c>
+      <c r="F33" s="31"/>
+      <c r="G33" s="32"/>
       <c r="H33" s="26" t="str">
         <f aca="false">IF(AND(B33="",OR(C33&lt;&gt;"",D33&lt;&gt;"",E33&lt;&gt;"",F33&lt;&gt;"",G33&lt;&gt;"")),"A lorry must be selected",IF(AND(C33="",OR(D33&lt;&gt;"",E33&lt;&gt;"",F33&lt;&gt;"",G33&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2220,18 +2208,26 @@
       <c r="J33" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="K33" s="34"/>
+      <c r="K33" s="34" t="n">
+        <v>3</v>
+      </c>
       <c r="L33" s="50" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="31"/>
+      <c r="B34" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="31" t="n">
+        <v>66</v>
+      </c>
       <c r="E34" s="31"/>
       <c r="F34" s="31"/>
       <c r="G34" s="32"/>
@@ -2246,21 +2242,27 @@
         <v>60</v>
       </c>
       <c r="K34" s="43" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L34" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B35" s="40"/>
-      <c r="C35" s="41"/>
+      <c r="B35" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>53</v>
+      </c>
       <c r="D35" s="31"/>
       <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
+      <c r="F35" s="31" t="n">
+        <v>33</v>
+      </c>
       <c r="G35" s="32"/>
       <c r="H35" s="26" t="str">
         <f aca="false">IF(AND(B35="",OR(C35&lt;&gt;"",D35&lt;&gt;"",E35&lt;&gt;"",F35&lt;&gt;"",G35&lt;&gt;"")),"A lorry must be selected",IF(AND(C35="",OR(D35&lt;&gt;"",E35&lt;&gt;"",F35&lt;&gt;"",G35&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2278,13 +2280,13 @@
         <v>28</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D36" s="31"/>
-      <c r="E36" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="F36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31" t="n">
+        <v>33</v>
+      </c>
       <c r="G36" s="32"/>
       <c r="H36" s="26" t="str">
         <f aca="false">IF(AND(B36="",OR(C36&lt;&gt;"",D36&lt;&gt;"",E36&lt;&gt;"",F36&lt;&gt;"",G36&lt;&gt;"")),"A lorry must be selected",IF(AND(C36="",OR(D36&lt;&gt;"",E36&lt;&gt;"",F36&lt;&gt;"",G36&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2295,18 +2297,12 @@
       <c r="A37" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B37" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="41" t="s">
-        <v>48</v>
-      </c>
+      <c r="B37" s="40"/>
+      <c r="C37" s="41"/>
       <c r="D37" s="31"/>
       <c r="E37" s="31"/>
       <c r="F37" s="31"/>
-      <c r="G37" s="32" t="n">
-        <v>25</v>
-      </c>
+      <c r="G37" s="32"/>
       <c r="H37" s="26" t="str">
         <f aca="false">IF(AND(B37="",OR(C37&lt;&gt;"",D37&lt;&gt;"",E37&lt;&gt;"",F37&lt;&gt;"",G37&lt;&gt;"")),"A lorry must be selected",IF(AND(C37="",OR(D37&lt;&gt;"",E37&lt;&gt;"",F37&lt;&gt;"",G37&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2322,17 +2318,17 @@
         <v>28</v>
       </c>
       <c r="B38" s="40" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" s="31"/>
+        <v>22</v>
+      </c>
+      <c r="D38" s="31" t="n">
+        <v>24</v>
+      </c>
       <c r="E38" s="31"/>
       <c r="F38" s="31"/>
-      <c r="G38" s="32" t="n">
-        <v>25</v>
-      </c>
+      <c r="G38" s="32"/>
       <c r="H38" s="26" t="str">
         <f aca="false">IF(AND(B38="",OR(C38&lt;&gt;"",D38&lt;&gt;"",E38&lt;&gt;"",F38&lt;&gt;"",G38&lt;&gt;"")),"A lorry must be selected",IF(AND(C38="",OR(D38&lt;&gt;"",E38&lt;&gt;"",F38&lt;&gt;"",G38&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2342,11 +2338,17 @@
       <c r="A39" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B39" s="40"/>
-      <c r="C39" s="41"/>
+      <c r="B39" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="41" t="s">
+        <v>49</v>
+      </c>
       <c r="D39" s="31"/>
       <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
+      <c r="F39" s="31" t="n">
+        <v>24</v>
+      </c>
       <c r="G39" s="32"/>
       <c r="H39" s="26" t="str">
         <f aca="false">IF(AND(B39="",OR(C39&lt;&gt;"",D39&lt;&gt;"",E39&lt;&gt;"",F39&lt;&gt;"",G39&lt;&gt;"")),"A lorry must be selected",IF(AND(C39="",OR(D39&lt;&gt;"",E39&lt;&gt;"",F39&lt;&gt;"",G39&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2361,15 +2363,15 @@
         <v>30</v>
       </c>
       <c r="B40" s="40" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C40" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31" t="n">
-        <v>38</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D40" s="31" t="n">
+        <v>24</v>
+      </c>
+      <c r="E40" s="31"/>
       <c r="F40" s="31"/>
       <c r="G40" s="32"/>
       <c r="H40" s="26" t="str">
@@ -2381,18 +2383,12 @@
       <c r="A41" s="54" t="n">
         <v>31</v>
       </c>
-      <c r="B41" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C41" s="41" t="s">
-        <v>39</v>
-      </c>
+      <c r="B41" s="40"/>
+      <c r="C41" s="41"/>
       <c r="D41" s="31"/>
       <c r="E41" s="31"/>
       <c r="F41" s="31"/>
-      <c r="G41" s="32" t="n">
-        <v>8</v>
-      </c>
+      <c r="G41" s="32"/>
       <c r="H41" s="26" t="str">
         <f aca="false">IF(AND(B41="",OR(C41&lt;&gt;"",D41&lt;&gt;"",E41&lt;&gt;"",F41&lt;&gt;"",G41&lt;&gt;"")),"A lorry must be selected",IF(AND(C41="",OR(D41&lt;&gt;"",E41&lt;&gt;"",F41&lt;&gt;"",G41&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2415,18 +2411,12 @@
       <c r="A42" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B42" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C42" s="41" t="s">
-        <v>42</v>
-      </c>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
       <c r="D42" s="31"/>
       <c r="E42" s="31"/>
       <c r="F42" s="31"/>
-      <c r="G42" s="32" t="n">
-        <v>10</v>
-      </c>
+      <c r="G42" s="32"/>
       <c r="H42" s="26" t="str">
         <f aca="false">IF(AND(B42="",OR(C42&lt;&gt;"",D42&lt;&gt;"",E42&lt;&gt;"",F42&lt;&gt;"",G42&lt;&gt;"")),"A lorry must be selected",IF(AND(C42="",OR(D42&lt;&gt;"",E42&lt;&gt;"",F42&lt;&gt;"",G42&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2446,18 +2436,12 @@
       <c r="A43" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B43" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C43" s="41" t="s">
-        <v>44</v>
-      </c>
+      <c r="B43" s="40"/>
+      <c r="C43" s="41"/>
       <c r="D43" s="31"/>
       <c r="E43" s="31"/>
       <c r="F43" s="31"/>
-      <c r="G43" s="32" t="n">
-        <v>20</v>
-      </c>
+      <c r="G43" s="32"/>
       <c r="H43" s="26" t="str">
         <f aca="false">IF(AND(B43="",OR(C43&lt;&gt;"",D43&lt;&gt;"",E43&lt;&gt;"",F43&lt;&gt;"",G43&lt;&gt;"")),"A lorry must be selected",IF(AND(C43="",OR(D43&lt;&gt;"",E43&lt;&gt;"",F43&lt;&gt;"",G43&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2494,26 +2478,20 @@
         <v>66</v>
       </c>
       <c r="K44" s="34" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="L44" s="57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B45" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C45" s="41" t="s">
-        <v>29</v>
-      </c>
+      <c r="B45" s="40"/>
+      <c r="C45" s="41"/>
       <c r="D45" s="31"/>
-      <c r="E45" s="31" t="n">
-        <v>30</v>
-      </c>
+      <c r="E45" s="31"/>
       <c r="F45" s="31"/>
       <c r="G45" s="32"/>
       <c r="H45" s="26" t="str">
@@ -2526,27 +2504,23 @@
       <c r="J45" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="K45" s="43"/>
+      <c r="K45" s="43" t="n">
+        <v>5</v>
+      </c>
       <c r="L45" s="58" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B46" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C46" s="41" t="s">
-        <v>45</v>
-      </c>
+      <c r="B46" s="40"/>
+      <c r="C46" s="41"/>
       <c r="D46" s="31"/>
       <c r="E46" s="31"/>
       <c r="F46" s="31"/>
-      <c r="G46" s="32" t="n">
-        <v>30</v>
-      </c>
+      <c r="G46" s="32"/>
       <c r="H46" s="26" t="str">
         <f aca="false">IF(AND(B46="",OR(C46&lt;&gt;"",D46&lt;&gt;"",E46&lt;&gt;"",F46&lt;&gt;"",G46&lt;&gt;"")),"A lorry must be selected",IF(AND(C46="",OR(D46&lt;&gt;"",E46&lt;&gt;"",F46&lt;&gt;"",G46&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2870,7 +2844,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="n">
         <v>58</v>
       </c>
@@ -2889,7 +2863,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="n">
         <v>59</v>
       </c>
@@ -2908,7 +2882,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="n">
         <v>60</v>
       </c>
@@ -2920,7 +2894,9 @@
       </c>
       <c r="D70" s="67"/>
       <c r="E70" s="68"/>
-      <c r="F70" s="68"/>
+      <c r="F70" s="68" t="n">
+        <v>24</v>
+      </c>
       <c r="G70" s="69"/>
       <c r="H70" s="26" t="str">
         <f aca="false">IF(AND(B70="",OR(C70&lt;&gt;"",D70&lt;&gt;"",E70&lt;&gt;"",F70&lt;&gt;"",G70&lt;&gt;"")),"A lorry must be selected",IF(AND(C70="",OR(D70&lt;&gt;"",E70&lt;&gt;"",F70&lt;&gt;"",G70&lt;&gt;"")),"A town must be selected",""))</f>
